--- a/data/trans_dic/IP16A09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,58</t>
+          <t>0,0; 20,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,4</t>
+          <t>0,0; 21,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,18</t>
+          <t>1,39; 14,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,29</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 12,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,5</t>
+          <t>0,0; 19,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,02</t>
+          <t>0,0; 18,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,26</t>
+          <t>0,0; 19,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>0,0; 11,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,71</t>
+          <t>0,0; 10,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,78</t>
+          <t>1,62; 15,17</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,48</t>
+          <t>0,0; 33,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,33</t>
+          <t>0,0; 16,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,01</t>
+          <t>0,0; 17,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,78</t>
+          <t>0,0; 22,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 31,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,58</t>
+          <t>1,56; 14,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,43</t>
+          <t>0,0; 12,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,18</t>
+          <t>0,0; 13,25</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 10,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,03</t>
+          <t>0,85; 9,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,33</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 7,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 6,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,15</t>
+          <t>0,77; 6,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,03</t>
+          <t>0,56; 5,16</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 21,59</t>
+          <t>2,65; 24,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,08</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,87</t>
+          <t>1,2; 9,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,26</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,49; 38,63</t>
+          <t>4,57; 38,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,49; 23,29</t>
+          <t>2,45; 23,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,93</t>
+          <t>2,38; 8,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,6</t>
+          <t>0,72; 4,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,39</t>
+          <t>0,36; 3,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,36</t>
+          <t>0,96; 5,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,02</t>
+          <t>1,47; 5,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,96</t>
+          <t>0,5; 4,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,56</t>
+          <t>1,95; 5,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,33</t>
+          <t>1,37; 4,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,1</t>
+          <t>0,81; 3,3</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2297</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3100</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4571</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>510; 5355</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1153</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2552</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3097</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3198</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3972</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3319</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4347</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4468</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4399</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>689; 6431</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1185</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3680</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2619</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3872</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4024</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3683</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>515; 4956</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4214</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3136</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2087</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1443</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3970</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>513; 6022</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3932</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3277</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5690</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2867</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4986</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1029; 8623</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>553; 5134</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1641</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1641</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>499; 4545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3283</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>512; 4089</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3078</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>662; 5562</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>644; 6044</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>8469</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>9083</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2613; 9301</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1275; 7897</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>568; 5248</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1295; 7564</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2631; 10281</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>698; 6394</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4775; 13437</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4880; 14808</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2405; 9803</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Clase-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,44</t>
+          <t>0,0; 20,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,3</t>
+          <t>0,0; 21,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 14,62</t>
+          <t>1,75; 15,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,22 +788,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>0,0; 16,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,48</t>
+          <t>0,0; 14,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,73</t>
+          <t>0,0; 17,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,59</t>
+          <t>0,0; 19,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,22 +813,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,53</t>
+          <t>0,0; 21,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,98</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 15,17</t>
+          <t>1,65; 13,77</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,12</t>
+          <t>0,0; 32,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,64</t>
+          <t>0,0; 14,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,08</t>
+          <t>0,0; 20,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,27</t>
+          <t>0,0; 29,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,99</t>
+          <t>1,57; 13,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>0,0; 13,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,25</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,53</t>
+          <t>0,0; 10,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,96</t>
+          <t>0,83; 10,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,45</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,82</t>
+          <t>0,0; 7,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,67</t>
+          <t>0,0; 8,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 5,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,47</t>
+          <t>0,9; 6,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,16</t>
+          <t>0,55; 5,01</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 24,11</t>
+          <t>2,68; 24,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 9,56</t>
+          <t>1,21; 10,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 38,42</t>
+          <t>4,42; 37,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 23,0</t>
+          <t>2,78; 25,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,48</t>
+          <t>2,37; 8,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,43</t>
+          <t>0,63; 4,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,36</t>
+          <t>0,38; 3,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,59</t>
+          <t>0,95; 5,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,75</t>
+          <t>1,42; 6,04</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,55</t>
+          <t>0,5; 5,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,48</t>
+          <t>1,81; 5,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,15</t>
+          <t>1,39; 4,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,3</t>
+          <t>0,83; 3,25</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3100</t>
+          <t>0; 3164</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4571</t>
+          <t>0; 4683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>510; 5355</t>
+          <t>642; 5785</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3097</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3198</t>
+          <t>0; 3807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3972</t>
+          <t>0; 3528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3319</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4347</t>
+          <t>0; 4792</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4468</t>
+          <t>0; 4097</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4399</t>
+          <t>0; 3873</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>689; 6431</t>
+          <t>701; 5835</t>
         </is>
       </c>
     </row>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3680</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,32 +1980,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3872</t>
+          <t>0; 3255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4024</t>
+          <t>0; 3661</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3683</t>
+          <t>0; 3474</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>515; 4956</t>
+          <t>519; 4530</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4214</t>
+          <t>0; 4560</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3136</t>
+          <t>0; 3540</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3970</t>
+          <t>0; 3946</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>513; 6022</t>
+          <t>502; 6079</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3932</t>
+          <t>0; 4155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3277</t>
+          <t>0; 3263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5690</t>
+          <t>0; 5658</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2867</t>
+          <t>0; 3552</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4986</t>
+          <t>0; 4403</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1029; 8623</t>
+          <t>1201; 8388</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>553; 5134</t>
+          <t>552; 4985</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>499; 4545</t>
+          <t>505; 4534</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 2951</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>512; 4089</t>
+          <t>516; 4484</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3078</t>
+          <t>0; 3247</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>662; 5562</t>
+          <t>640; 5432</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>644; 6044</t>
+          <t>729; 6585</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2613; 9301</t>
+          <t>2596; 9867</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1275; 7897</t>
+          <t>1123; 7630</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>568; 5248</t>
+          <t>601; 5367</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1295; 7564</t>
+          <t>1291; 7172</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2631; 10281</t>
+          <t>2544; 10814</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>698; 6394</t>
+          <t>703; 7029</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4775; 13437</t>
+          <t>4441; 13527</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4880; 14808</t>
+          <t>4958; 14855</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2405; 9803</t>
+          <t>2463; 9645</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A09-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,36%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,86</t>
+          <t>0,0; 19,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,82</t>
+          <t>0,0; 20,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,79</t>
+          <t>1,75; 15,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>3,07%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,73%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,2</t>
+          <t>0,0; 16,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,53</t>
+          <t>0,0; 19,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,72</t>
+          <t>0,0; 18,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,53</t>
+          <t>0,0; 17,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 13,77</t>
+          <t>1,6; 13,78</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>10,67%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>3,93%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,4</t>
+          <t>0,0; 12,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>0,0; 19,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 25,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,83</t>
+          <t>0,0; 33,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,09</t>
+          <t>0,0; 17,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,7</t>
+          <t>1,53; 13,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,34</t>
+          <t>0,0; 12,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 15,18</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,47</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 10,05</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,41</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,78</t>
+          <t>0,82; 9,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,26</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,76</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,3</t>
+          <t>0,97; 6,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,01</t>
+          <t>0,55; 5,03</t>
         </is>
       </c>
     </row>
@@ -1065,27 +1065,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,7%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 24,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,67; 21,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,49</t>
+          <t>1,2; 10,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 5,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>18,26%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>4,49; 38,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 37,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 25,07</t>
+          <t>2,49; 23,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,74%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,46%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,99</t>
+          <t>0,96; 5,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,28</t>
+          <t>1,45; 6,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,43</t>
+          <t>0,5; 4,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,3</t>
+          <t>2,54; 8,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,04</t>
+          <t>0,68; 4,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,01</t>
+          <t>0,37; 3,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,52</t>
+          <t>2,02; 5,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,16</t>
+          <t>1,44; 4,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,25</t>
+          <t>0,74; 3,1</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1586,22 +1586,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1333</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>965</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3164</t>
+          <t>0; 4163</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4683</t>
+          <t>0; 3122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>642; 5785</t>
+          <t>641; 5559</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1701,22 +1701,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1153</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 2862</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3807</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3528</t>
+          <t>0; 4287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3521</t>
+          <t>0; 3555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3836</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4792</t>
+          <t>0; 3522</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4097</t>
+          <t>0; 3882</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3873</t>
+          <t>0; 3934</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>701; 5835</t>
+          <t>678; 5840</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1185</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 2636</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3004</t>
+          <t>0; 3604</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3027</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3255</t>
+          <t>0; 3720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3661</t>
+          <t>0; 2766</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3474</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>519; 4530</t>
+          <t>506; 4491</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4560</t>
+          <t>0; 4249</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 3591</t>
         </is>
       </c>
     </row>
@@ -2027,27 +2027,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2087</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1124</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1620</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>502; 6079</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4155</t>
+          <t>0; 3425</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3263</t>
+          <t>0; 4457</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5658</t>
+          <t>494; 5463</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3552</t>
+          <t>0; 3453</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4403</t>
+          <t>0; 4504</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1201; 8388</t>
+          <t>1288; 8188</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>552; 4985</t>
+          <t>548; 5009</t>
         </is>
       </c>
     </row>
@@ -2185,27 +2185,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2238,27 +2238,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1641</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>505; 4534</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>504; 4070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>516; 4484</t>
+          <t>513; 4647</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3247</t>
+          <t>0; 3747</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>649; 5592</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>640; 5432</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>729; 6585</t>
+          <t>655; 6117</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,27 +2511,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>2277</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2596; 9867</t>
+          <t>1294; 7246</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1123; 7630</t>
+          <t>2601; 10773</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>601; 5367</t>
+          <t>705; 6968</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1291; 7172</t>
+          <t>2792; 9799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2544; 10814</t>
+          <t>1219; 8199</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>703; 7029</t>
+          <t>572; 5307</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4441; 13527</t>
+          <t>4953; 13620</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4958; 14855</t>
+          <t>5133; 15481</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2463; 9645</t>
+          <t>2189; 9194</t>
         </is>
       </c>
     </row>
